--- a/Assets/Samples/FacebookDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/FacebookDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SoloGames-X\nova\Assets\Samples\FacebookDemo\Excels\Networks\Cmds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F699B8DD-E305-4B0A-BAF0-FD70021416DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3359506-A207-431A-9BD5-EB7547D6F031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="26863" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkCmds" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>##comment</t>
   </si>
@@ -67,6 +67,48 @@
     <t>路径</t>
   </si>
   <si>
+    <t>GameAccountLogin</t>
+  </si>
+  <si>
+    <t>游戏登录</t>
+  </si>
+  <si>
+    <t>HTTP_POST</t>
+  </si>
+  <si>
+    <t>GameServer</t>
+  </si>
+  <si>
+    <t>/v1/user/loginV1</t>
+  </si>
+  <si>
+    <t>GameAccountBind</t>
+  </si>
+  <si>
+    <t>绑定</t>
+  </si>
+  <si>
+    <t>/v1/account/bind</t>
+  </si>
+  <si>
+    <t>GameAccountBindConflict</t>
+  </si>
+  <si>
+    <t>绑定冲突查询</t>
+  </si>
+  <si>
+    <t>/v1/account/bind/conflict</t>
+  </si>
+  <si>
+    <t>GameAccountBindResolve</t>
+  </si>
+  <si>
+    <t>绑定裁决</t>
+  </si>
+  <si>
+    <t>/v1/account/bind/resolve</t>
+  </si>
+  <si>
     <t>TGAServerUrl</t>
   </si>
   <si>
@@ -77,21 +119,6 @@
   </si>
   <si>
     <t>TGAServer</t>
-  </si>
-  <si>
-    <t>GameAccountLogin</t>
-  </si>
-  <si>
-    <t>游戏登录</t>
-  </si>
-  <si>
-    <t>HTTP_POST</t>
-  </si>
-  <si>
-    <t>GameServer</t>
-  </si>
-  <si>
-    <t>/v1/user/loginV1</t>
   </si>
 </sst>
 </file>
@@ -205,27 +232,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,14 +560,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37" style="2" customWidth="1"/>
-    <col min="3" max="3" width="44.3046875" style="2" customWidth="1"/>
-    <col min="4" max="21" width="37" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="13" style="3"/>
+    <col min="2" max="21" width="37" style="3" customWidth="1"/>
+    <col min="22" max="22" width="13" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="13" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -658,40 +687,152 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="8" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+    </row>
     <row r="10" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -723,6 +864,11 @@
     <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="40" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Samples/FacebookDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/FacebookDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -559,9 +559,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U45"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.15" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="21" width="37" style="3" customWidth="1"/>
@@ -569,7 +569,7 @@
     <col min="23" max="16384" width="13" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -631,7 +631,7 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -666,7 +666,7 @@
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
     </row>
-    <row r="4" spans="1:21" s="1" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
@@ -703,7 +703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" customFormat="1" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -736,7 +736,7 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
     </row>
-    <row r="7" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" customFormat="1" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
         <v>23</v>
@@ -769,7 +769,7 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
     </row>
-    <row r="8" spans="1:21" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" customFormat="1" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
         <v>26</v>
@@ -802,7 +802,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
     </row>
-    <row r="9" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="8" t="s">
         <v>29</v>
@@ -833,42 +833,68 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="22" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>AppCustomConfig</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>拉取GM后台应用配置URL</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>HTTP_POST</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>/v1/common/app-config</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="12" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="13" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="14" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="15" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="16" spans="1:21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="17" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="18" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="19" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="20" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="21" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="22" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="23" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="24" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="25" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="26" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="27" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="28" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="29" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="30" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="31" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="32" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="33" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="34" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="35" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="36" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="37" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="38" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="39" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="40" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="41" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="42" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="43" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="44" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
+    <row r="45" ht="22" customHeight="1" ns3:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
